--- a/orcamento-marcenaria/config/tabela_precos_referencia.xlsx
+++ b/orcamento-marcenaria/config/tabela_precos_referencia.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0.00;($#,##0.00);-"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,6 +43,10 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="00000000"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -89,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -99,7 +103,8 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -465,19 +470,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -487,10 +494,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="40" customHeight="1">
+    <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Preencha 1 linha por REFERENCE (codigo que aparece no XML/DXF exportado do Promob). O extractor casa o campo 'reference' do item extraido com a coluna REFERENCE aqui para descobrir o preco de venda ou custo do material/acabamento. Codigo Interno e o seu codigo proprio de controle (opcional). Espessura e extraida automaticamente do REFERENCE quando possivel, mas pode ser corrigida manualmente.</t>
+          <t>MUDANCA DE MODELO: agora chapas de MDF sao precificadas por CHAPA FECHADA (nao mais por m2 da peca), e fita de borda por METRO. As linhas abaixo foram migradas do formato antigo -- o preco por m2 anterior ficou salvo em Observacoes como referencia, mas voce precisa preencher 'Preco Chapa Fechada' e 'Preco Fita de Borda' com os valores reais (nao foram calculados automaticamente para evitar inventar preco).</t>
         </is>
       </c>
     </row>
@@ -527,20 +534,30 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Preco Unitario (R$)</t>
+          <t>Preco Unitario UN (R$)</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
+          <t>Preco Chapa Fechada (R$)</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Preco Fita de Borda (R$/m)</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
           <t>Fornecedor</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Data Atualizacao</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Observacoes</t>
         </is>
@@ -552,7 +569,7 @@
           <t>2.0835.18.Duratex.Essencial.Rosa Infinito</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr"/>
+      <c r="B5" s="5" t="n"/>
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t>MDF 18mm Duratex Essencial Rosa Infinito</t>
@@ -571,22 +588,22 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="G5" s="5" t="n">
-        <v>591.9</v>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="6" t="n"/>
+      <c r="I5" s="6" t="n"/>
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>Léo Madeiras</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>27/08/2026</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>Exemplo - preencha com seus precos reais</t>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>[MIGRADO] Preco antigo por m2 (formato anterior): R$591.90/m2 -- preencha o preco real da CHAPA FECHADA e da FITA abaixo.</t>
         </is>
       </c>
     </row>
@@ -596,7 +613,7 @@
           <t>1.2235.4.Berneck.Unicolors Metallic Suede TX</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
+      <c r="B6" s="5" t="n"/>
       <c r="C6" s="4" t="inlineStr">
         <is>
           <t>MDF 6mm Berneck.Unicolors Metallic Suede TX</t>
@@ -615,20 +632,24 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="G6" s="5" t="n">
-        <v>339.9</v>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="G6" s="6" t="n"/>
+      <c r="H6" s="6" t="n"/>
+      <c r="I6" s="6" t="n"/>
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>Léo Madeiras</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>27/08/2027</t>
         </is>
       </c>
-      <c r="J6" s="4" t="n"/>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>[MIGRADO] Preco antigo por m2 (formato anterior): R$339.90/m2 -- preencha o preco real da CHAPA FECHADA e da FITA abaixo.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -636,7 +657,7 @@
           <t>1.0394.18.Berneck.Unicolors Metallic Suede TX.MDF</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr"/>
+      <c r="B7" s="5" t="n"/>
       <c r="C7" s="4" t="inlineStr">
         <is>
           <t>MDF 18 mm Berneck.Unicolors Metallic Suede TX</t>
@@ -655,20 +676,24 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="G7" s="5" t="n">
-        <v>535.9</v>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="G7" s="6" t="n"/>
+      <c r="H7" s="6" t="n"/>
+      <c r="I7" s="6" t="n"/>
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>Léo Madeiras</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>27/08/2028</t>
         </is>
       </c>
-      <c r="J7" s="4" t="n"/>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>[MIGRADO] Preco antigo por m2 (formato anterior): R$535.90/m2 -- preencha o preco real da CHAPA FECHADA e da FITA abaixo.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -676,7 +701,7 @@
           <t>2.2054.15.Branco TX.MDF</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr"/>
+      <c r="B8" s="5" t="n"/>
       <c r="C8" s="4" t="inlineStr">
         <is>
           <t>MDF 15mm Branco TX</t>
@@ -695,20 +720,24 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="G8" s="5" t="n">
-        <v>259.9</v>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="G8" s="6" t="n"/>
+      <c r="H8" s="6" t="n"/>
+      <c r="I8" s="6" t="n"/>
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>Léo Madeiras</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="K8" s="4" t="inlineStr">
         <is>
           <t>27/08/2029</t>
         </is>
       </c>
-      <c r="J8" s="4" t="n"/>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>[MIGRADO] Preco antigo por m2 (formato anterior): R$259.90/m2 -- preencha o preco real da CHAPA FECHADA e da FITA abaixo.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -716,7 +745,7 @@
           <t>2.2032.18.Branco TX.MDF</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr"/>
+      <c r="B9" s="5" t="n"/>
       <c r="C9" s="4" t="inlineStr">
         <is>
           <t>MDF 18mm Branco TX</t>
@@ -735,20 +764,24 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="G9" s="5" t="n">
-        <v>334.9</v>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="6" t="n"/>
+      <c r="I9" s="6" t="n"/>
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>Léo Madeiras</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>27/08/2030</t>
         </is>
       </c>
-      <c r="J9" s="4" t="n"/>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>[MIGRADO] Preco antigo por m2 (formato anterior): R$334.90/m2 -- preencha o preco real da CHAPA FECHADA e da FITA abaixo.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -756,7 +789,7 @@
           <t>2.2056.9.Branco.MDF</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr"/>
+      <c r="B10" s="5" t="n"/>
       <c r="C10" s="4" t="inlineStr">
         <is>
           <t>MDF 9mm Branco TX</t>
@@ -775,20 +808,24 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="G10" s="5" t="n">
-        <v>253.9</v>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="6" t="n"/>
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>Léo Madeiras</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="K10" s="4" t="inlineStr">
         <is>
           <t>27/08/2031</t>
         </is>
       </c>
-      <c r="J10" s="4" t="n"/>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>[MIGRADO] Preco antigo por m2 (formato anterior): R$253.90/m2 -- preencha o preco real da CHAPA FECHADA e da FITA abaixo.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -796,7 +833,7 @@
           <t>2.2018.18.Duratex.Essencial.Rosa Infinito.MDF</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr"/>
+      <c r="B11" s="5" t="n"/>
       <c r="C11" s="4" t="inlineStr">
         <is>
           <t>MDF 18mm Duratex Essencial Rosa Infinito</t>
@@ -815,265 +852,309 @@
           <t>M2</t>
         </is>
       </c>
-      <c r="G11" s="5" t="n">
-        <v>591.9</v>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
+      <c r="I11" s="6" t="n"/>
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>Léo Madeiras</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>27/08/2032</t>
         </is>
       </c>
-      <c r="J11" s="4" t="n"/>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>[MIGRADO] Preco antigo por m2 (formato anterior): R$591.90/m2 -- preencha o preco real da CHAPA FECHADA e da FITA abaixo.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n"/>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="5" t="n"/>
-      <c r="H12" s="4" t="n"/>
-      <c r="I12" s="4" t="n"/>
-      <c r="J12" s="4" t="n"/>
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="5" t="n"/>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="6" t="n"/>
+      <c r="H12" s="6" t="n"/>
+      <c r="I12" s="6" t="n"/>
+      <c r="J12" s="5" t="n"/>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="n"/>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="4" t="n"/>
-      <c r="I13" s="4" t="n"/>
-      <c r="J13" s="4" t="n"/>
+      <c r="A13" s="5" t="n"/>
+      <c r="B13" s="5" t="n"/>
+      <c r="C13" s="5" t="n"/>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="6" t="n"/>
+      <c r="J13" s="5" t="n"/>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n"/>
-      <c r="J14" s="4" t="n"/>
+      <c r="A14" s="5" t="n"/>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="6" t="n"/>
+      <c r="H14" s="6" t="n"/>
+      <c r="I14" s="6" t="n"/>
+      <c r="J14" s="5" t="n"/>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="5" t="n"/>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="n"/>
-      <c r="J15" s="4" t="n"/>
+      <c r="A15" s="5" t="n"/>
+      <c r="B15" s="5" t="n"/>
+      <c r="C15" s="5" t="n"/>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="6" t="n"/>
+      <c r="J15" s="5" t="n"/>
+      <c r="K15" s="5" t="n"/>
+      <c r="L15" s="5" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n"/>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="n"/>
-      <c r="J16" s="4" t="n"/>
+      <c r="A16" s="5" t="n"/>
+      <c r="B16" s="5" t="n"/>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="6" t="n"/>
+      <c r="J16" s="5" t="n"/>
+      <c r="K16" s="5" t="n"/>
+      <c r="L16" s="5" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n"/>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="4" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="4" t="n"/>
-      <c r="I17" s="4" t="n"/>
-      <c r="J17" s="4" t="n"/>
+      <c r="A17" s="5" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="6" t="n"/>
+      <c r="H17" s="6" t="n"/>
+      <c r="I17" s="6" t="n"/>
+      <c r="J17" s="5" t="n"/>
+      <c r="K17" s="5" t="n"/>
+      <c r="L17" s="5" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="4" t="n"/>
-      <c r="G18" s="5" t="n"/>
-      <c r="H18" s="4" t="n"/>
-      <c r="I18" s="4" t="n"/>
-      <c r="J18" s="4" t="n"/>
+      <c r="A18" s="5" t="n"/>
+      <c r="B18" s="5" t="n"/>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="6" t="n"/>
+      <c r="H18" s="6" t="n"/>
+      <c r="I18" s="6" t="n"/>
+      <c r="J18" s="5" t="n"/>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n"/>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="4" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="4" t="n"/>
-      <c r="I19" s="4" t="n"/>
-      <c r="J19" s="4" t="n"/>
+      <c r="A19" s="5" t="n"/>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+      <c r="I19" s="6" t="n"/>
+      <c r="J19" s="5" t="n"/>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n"/>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="4" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="4" t="n"/>
-      <c r="I20" s="4" t="n"/>
-      <c r="J20" s="4" t="n"/>
+      <c r="A20" s="5" t="n"/>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="6" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n"/>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
-      <c r="G21" s="5" t="n"/>
-      <c r="H21" s="4" t="n"/>
-      <c r="I21" s="4" t="n"/>
-      <c r="J21" s="4" t="n"/>
+      <c r="A21" s="5" t="n"/>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="6" t="n"/>
+      <c r="J21" s="5" t="n"/>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n"/>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="4" t="n"/>
-      <c r="I22" s="4" t="n"/>
-      <c r="J22" s="4" t="n"/>
+      <c r="A22" s="5" t="n"/>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="6" t="n"/>
+      <c r="H22" s="6" t="n"/>
+      <c r="I22" s="6" t="n"/>
+      <c r="J22" s="5" t="n"/>
+      <c r="K22" s="5" t="n"/>
+      <c r="L22" s="5" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n"/>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="4" t="n"/>
-      <c r="I23" s="4" t="n"/>
-      <c r="J23" s="4" t="n"/>
+      <c r="A23" s="5" t="n"/>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="6" t="n"/>
+      <c r="J23" s="5" t="n"/>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="5" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n"/>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="4" t="n"/>
-      <c r="I24" s="4" t="n"/>
-      <c r="J24" s="4" t="n"/>
+      <c r="A24" s="5" t="n"/>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="6" t="n"/>
+      <c r="H24" s="6" t="n"/>
+      <c r="I24" s="6" t="n"/>
+      <c r="J24" s="5" t="n"/>
+      <c r="K24" s="5" t="n"/>
+      <c r="L24" s="5" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n"/>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="4" t="n"/>
-      <c r="G25" s="5" t="n"/>
-      <c r="H25" s="4" t="n"/>
-      <c r="I25" s="4" t="n"/>
-      <c r="J25" s="4" t="n"/>
+      <c r="A25" s="5" t="n"/>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="6" t="n"/>
+      <c r="H25" s="6" t="n"/>
+      <c r="I25" s="6" t="n"/>
+      <c r="J25" s="5" t="n"/>
+      <c r="K25" s="5" t="n"/>
+      <c r="L25" s="5" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n"/>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="n"/>
-      <c r="F26" s="4" t="n"/>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="4" t="n"/>
-      <c r="I26" s="4" t="n"/>
-      <c r="J26" s="4" t="n"/>
+      <c r="A26" s="5" t="n"/>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="6" t="n"/>
+      <c r="J26" s="5" t="n"/>
+      <c r="K26" s="5" t="n"/>
+      <c r="L26" s="5" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n"/>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="4" t="n"/>
-      <c r="G27" s="5" t="n"/>
-      <c r="H27" s="4" t="n"/>
-      <c r="I27" s="4" t="n"/>
-      <c r="J27" s="4" t="n"/>
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="5" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="6" t="n"/>
+      <c r="H27" s="6" t="n"/>
+      <c r="I27" s="6" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="n"/>
+      <c r="L27" s="5" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="n"/>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="4" t="n"/>
-      <c r="G28" s="5" t="n"/>
-      <c r="H28" s="4" t="n"/>
-      <c r="I28" s="4" t="n"/>
-      <c r="J28" s="4" t="n"/>
+      <c r="A28" s="5" t="n"/>
+      <c r="B28" s="5" t="n"/>
+      <c r="C28" s="5" t="n"/>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="6" t="n"/>
+      <c r="J28" s="5" t="n"/>
+      <c r="K28" s="5" t="n"/>
+      <c r="L28" s="5" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n"/>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="4" t="n"/>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="n"/>
-      <c r="F29" s="4" t="n"/>
-      <c r="G29" s="5" t="n"/>
-      <c r="H29" s="4" t="n"/>
-      <c r="I29" s="4" t="n"/>
-      <c r="J29" s="4" t="n"/>
+      <c r="A29" s="5" t="n"/>
+      <c r="B29" s="5" t="n"/>
+      <c r="C29" s="5" t="n"/>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="6" t="n"/>
+      <c r="H29" s="6" t="n"/>
+      <c r="I29" s="6" t="n"/>
+      <c r="J29" s="5" t="n"/>
+      <c r="K29" s="5" t="n"/>
+      <c r="L29" s="5" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="n"/>
-      <c r="B30" s="4" t="n"/>
-      <c r="C30" s="4" t="n"/>
-      <c r="D30" s="4" t="n"/>
-      <c r="E30" s="4" t="n"/>
-      <c r="F30" s="4" t="n"/>
-      <c r="G30" s="5" t="n"/>
-      <c r="H30" s="4" t="n"/>
-      <c r="I30" s="4" t="n"/>
-      <c r="J30" s="4" t="n"/>
+      <c r="A30" s="5" t="n"/>
+      <c r="B30" s="5" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n"/>
+      <c r="I30" s="6" t="n"/>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="5" t="n"/>
+      <c r="L30" s="5" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n"/>
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="n"/>
-      <c r="F31" s="4" t="n"/>
-      <c r="G31" s="5" t="n"/>
-      <c r="H31" s="4" t="n"/>
-      <c r="I31" s="4" t="n"/>
-      <c r="J31" s="4" t="n"/>
+      <c r="A31" s="5" t="n"/>
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="6" t="n"/>
+      <c r="H31" s="6" t="n"/>
+      <c r="I31" s="6" t="n"/>
+      <c r="J31" s="5" t="n"/>
+      <c r="K31" s="5" t="n"/>
+      <c r="L31" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/orcamento-marcenaria/config/tabela_precos_referencia.xlsx
+++ b/orcamento-marcenaria/config/tabela_precos_referencia.xlsx
@@ -1068,15 +1068,37 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n"/>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>2.2008.18.Branco.MDF</t>
+        </is>
+      </c>
       <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>MDF 18mm Branco TX</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Chapa MDF</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
       <c r="G20" s="8" t="n"/>
-      <c r="H20" s="8" t="n"/>
-      <c r="I20" s="8" t="n"/>
+      <c r="H20" s="8" t="n">
+        <v>334.9</v>
+      </c>
+      <c r="I20" s="8" t="n">
+        <v>26.9</v>
+      </c>
       <c r="J20" s="5" t="n"/>
       <c r="K20" s="5" t="n"/>
       <c r="L20" s="5" t="n"/>
